--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104497_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104497_W5.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.253500000000001</v>
+        <v>7.3658</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4749</v>
+        <v>7.5005</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2213</v>
+        <v>-0.1348</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3329</v>
+        <v>5.3147</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2801</v>
+        <v>4.2631</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0529</v>
+        <v>1.0516</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2601</v>
+        <v>6.2302</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6582</v>
+        <v>4.6367</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9272</v>
+        <v>-0.9155</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>2.174</v>
+        <v>1.2983</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2562</v>
+        <v>1.319</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9365</v>
+        <v>6.4999</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0003</v>
+        <v>7.3843</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0638</v>
+        <v>-0.8844</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6351</v>
+        <v>3.6186</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7374</v>
+        <v>1.7349</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8977</v>
+        <v>1.8837</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8977</v>
+        <v>5.8657</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8009</v>
+        <v>1.7926</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0967</v>
+        <v>4.073</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2626</v>
+        <v>-2.2471</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9935</v>
+        <v>-0.4147</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3115</v>
+        <v>0.1136</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.5283</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.467</v>
+        <v>3.6459</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7813</v>
+        <v>3.3105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6857</v>
+        <v>0.3354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.189</v>
+        <v>0.1931</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4315</v>
+        <v>0.4281</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2425</v>
+        <v>-0.235</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2834</v>
+        <v>2.269</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0146</v>
+        <v>1.003</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0944</v>
+        <v>-2.0759</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4633</v>
+        <v>0.6317</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0484</v>
+        <v>0.4967</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5117</v>
+        <v>0.135</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0781</v>
+        <v>1.2094</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4513</v>
+        <v>1.0123</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3731</v>
+        <v>0.1971</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6597</v>
+        <v>-1.8786</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1284</v>
+        <v>0.0461</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4687</v>
+        <v>-1.9247</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5541</v>
+        <v>0.425</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2555</v>
+        <v>0.2618</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2985</v>
+        <v>0.1632</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8944</v>
+        <v>-2.3036</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1272</v>
+        <v>-0.2157</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7672</v>
+        <v>-2.0879</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4942</v>
+        <v>0.5841</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6684</v>
+        <v>0.5874</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1742</v>
+        <v>-0.0033</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.1173</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7157</v>
+        <v>0.52</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4196</v>
+        <v>0.5665</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7039</v>
+        <v>-0.0466</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5407999999999999</v>
+        <v>-1.6285</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3435</v>
+        <v>-0.0568</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1973</v>
+        <v>-1.5716</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0838</v>
+        <v>-0.4828</v>
       </c>
       <c r="K6" t="n">
-        <v>0.218</v>
+        <v>0.389</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8658</v>
+        <v>-0.8718</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5431</v>
+        <v>-1.1457</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1255</v>
+        <v>-0.4458</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6685</v>
+        <v>-0.6998</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3188</v>
+        <v>-0.9897</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3357</v>
+        <v>-0.1979</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0169</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4987</v>
+        <v>0.4395</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6087</v>
+        <v>2.2435</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.11</v>
+        <v>-1.804</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8728</v>
+        <v>0.542</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0491</v>
+        <v>0.3391</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9219</v>
+        <v>0.2028</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4484</v>
+        <v>2.0719</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27</v>
+        <v>0.2101</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1785</v>
+        <v>1.8618</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3212</v>
+        <v>-1.53</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2209</v>
+        <v>0.129</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1003</v>
+        <v>-1.659</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1237</v>
+        <v>0.0278</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1603</v>
+        <v>0.1716</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.284</v>
+        <v>-0.1438</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4608</v>
+        <v>0.1428</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7197</v>
+        <v>2.6085</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2588</v>
+        <v>-2.4657</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.616</v>
+        <v>1.6625</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.046</v>
+        <v>3.125</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.57</v>
+        <v>-1.4625</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4521</v>
+        <v>3.5384</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4116</v>
+        <v>3.2405</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8637</v>
+        <v>0.2979</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1639</v>
+        <v>-1.8759</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4576</v>
+        <v>-0.1155</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7063</v>
+        <v>-1.7604</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0573</v>
+        <v>-0.4577</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.156</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9757</v>
+        <v>-0.3017</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-3.1107</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2534</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1058</v>
+        <v>-0.4385</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5909</v>
+        <v>-1.2194</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6967</v>
+        <v>0.7809</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3847</v>
+        <v>-3.4064</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0386</v>
+        <v>-2.0582</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3461</v>
+        <v>-1.3482</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8953</v>
+        <v>-1.9317</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6287</v>
+        <v>-1.6557</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4894</v>
+        <v>-1.4747</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.3761</v>
       </c>
       <c r="T9" t="n">
-        <v>0.983</v>
+        <v>0.3968</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1682</v>
+        <v>-1.1711</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.995</v>
+        <v>-0.9988</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8023</v>
+        <v>-0.8041</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6291</v>
+        <v>-0.6317</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.366</v>
+        <v>-0.367</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8158</v>
+        <v>-1.9567</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9054</v>
+        <v>-0.3017</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0897</v>
+        <v>-1.655</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5869</v>
+        <v>-0.8637</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3421</v>
+        <v>1.0058</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2449</v>
+        <v>-1.8695</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0757</v>
+        <v>0.795</v>
       </c>
       <c r="K11" t="n">
-        <v>0.052</v>
+        <v>1.2648</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1276</v>
+        <v>-0.4698</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5113</v>
+        <v>-1.6587</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.394</v>
+        <v>-0.259</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1172</v>
+        <v>-1.3997</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7752</v>
+        <v>-0.2312</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6956</v>
+        <v>0.0902</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0796</v>
+        <v>-0.3213</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9236</v>
+        <v>-2.8055</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3904</v>
+        <v>-2.6867</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5332</v>
+        <v>-0.1188</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8525</v>
+        <v>-1.5895</v>
       </c>
       <c r="H12" t="n">
-        <v>1.016</v>
+        <v>-0.3363</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8685</v>
+        <v>-1.2531</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8286</v>
+        <v>-1.0884</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2845</v>
+        <v>0.0517</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4559</v>
+        <v>-1.1401</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6812</v>
+        <v>-0.5011</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2685</v>
+        <v>-0.3881</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4126</v>
+        <v>-0.113</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2052</v>
+        <v>-0.7608</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0434</v>
+        <v>-0.4601</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1618</v>
+        <v>-0.3006</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3455</v>
+        <v>-2.8634</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.309</v>
+        <v>-3.1071</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0364</v>
+        <v>0.2437</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6477</v>
+        <v>-3.6627</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.2074</v>
+        <v>-4.2212</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5598</v>
+        <v>0.5586</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1265</v>
+        <v>-2.1591</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.7657</v>
+        <v>-3.7898</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5212</v>
+        <v>-1.5036</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5105</v>
+        <v>-0.0234</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0484</v>
+        <v>0.1901</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4621</v>
+        <v>-0.2135</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.263</v>
+        <v>10.5881</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2651</v>
+        <v>16.3124</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.001600000000001</v>
+        <v>-5.724600000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.405399999999999</v>
+        <v>-2.502600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4.178700000000001</v>
+        <v>4.097200000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.584</v>
+        <v>-6.599600000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>15.0201</v>
+        <v>14.7436</v>
       </c>
       <c r="K14" t="n">
-        <v>7.570899999999997</v>
+        <v>7.4047</v>
       </c>
       <c r="L14" t="n">
-        <v>7.449199999999999</v>
+        <v>7.339000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-17.4258</v>
+        <v>-17.2462</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.3923</v>
+        <v>-3.3077</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.0331</v>
+        <v>-13.9386</v>
       </c>
       <c r="P14" t="n">
-        <v>17.0124</v>
+        <v>17.0723</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.6709</v>
+        <v>-5.690900000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6833</v>
+        <v>22.7631</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6804000000000001</v>
+        <v>-0.3264999999999997</v>
       </c>
       <c r="T14" t="n">
-        <v>1.966</v>
+        <v>2.3423</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6465</v>
+        <v>-2.6686</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.6636</v>
+        <v>-3.6555</v>
       </c>
       <c r="W14" t="n">
-        <v>4.949400000000001</v>
+        <v>4.9175</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.6129</v>
+        <v>-8.572800000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8796</v>
+        <v>6.5473</v>
       </c>
       <c r="E15" t="n">
-        <v>8.052199999999999</v>
+        <v>8.241199999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1726</v>
+        <v>-1.6939</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9914</v>
+        <v>2.9944</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8572</v>
+        <v>-1.8527</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8486</v>
+        <v>4.8471</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7511</v>
+        <v>5.7146</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L15" t="n">
-        <v>6.3785</v>
+        <v>6.3598</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7596</v>
+        <v>-2.7202</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2298</v>
+        <v>-1.2075</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5299</v>
+        <v>-1.5127</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6847</v>
+        <v>-0.0115</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0212</v>
+        <v>0.2598</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7059</v>
+        <v>-0.2713</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2055</v>
+        <v>1.7272</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0111</v>
+        <v>1.7806</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1943</v>
+        <v>-0.0534</v>
       </c>
       <c r="G16" t="n">
-        <v>0.521</v>
+        <v>2.4286</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5901999999999999</v>
+        <v>-0.7365</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0692</v>
+        <v>3.1651</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0826</v>
+        <v>3.1855</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8587</v>
+        <v>0.1551</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2239</v>
+        <v>3.0304</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5617</v>
+        <v>-0.7569</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2685</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2931</v>
+        <v>0.1347</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6184</v>
+        <v>0.6856</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1553</v>
+        <v>0.1901</v>
       </c>
       <c r="U16" t="n">
-        <v>0.463</v>
+        <v>0.4955</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0395</v>
+        <v>1.4812</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5734</v>
+        <v>1.294</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4661</v>
+        <v>0.1872</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4126</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7594</v>
+        <v>0.5888</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1719</v>
+        <v>-0.0591</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2077</v>
+        <v>1.0713</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1559</v>
+        <v>0.8479</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0519</v>
+        <v>0.2234</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7951</v>
+        <v>-0.5416</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9152</v>
+        <v>-0.259</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1201</v>
+        <v>-0.2826</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0126</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0484</v>
+        <v>0.4504</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0609</v>
+        <v>0.4313</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7071</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1321</v>
+        <v>0.4528</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1306</v>
+        <v>-1.1632</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2626</v>
+        <v>1.6159</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1932</v>
+        <v>2.2071</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7299</v>
+        <v>0.7459</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4634</v>
+        <v>1.4612</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0189</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1743</v>
+        <v>1.2076</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2225</v>
+        <v>-0.2022</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1785</v>
+        <v>0.135</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1603</v>
+        <v>0.1623</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3388</v>
+        <v>-0.0273</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2744</v>
+        <v>0.3665</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1452</v>
+        <v>2.4818</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4196</v>
+        <v>-2.1153</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8778</v>
+        <v>-0.868</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4993</v>
+        <v>-0.4943</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3785</v>
+        <v>-0.3737</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.103</v>
+        <v>-0.1091</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7749</v>
+        <v>-0.7588</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8768</v>
+        <v>-0.2404</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4594</v>
+        <v>-0.1775</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W19" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.1539</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.895</v>
+        <v>-0.6691</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2534</v>
+        <v>0.5152</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2075</v>
+        <v>-0.2005</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.658</v>
+        <v>-0.655</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4505</v>
+        <v>0.4545</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7144</v>
+        <v>-0.7179</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5069</v>
+        <v>0.5174</v>
       </c>
       <c r="N20" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6194</v>
+        <v>-0.1323</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1391</v>
+        <v>0.0975</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4803</v>
+        <v>-0.2298</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9596</v>
+        <v>-1.1997</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5992</v>
+        <v>-1.5874</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3605</v>
+        <v>0.3877</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0498</v>
+        <v>1.5803</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6912</v>
+        <v>-0.1043</v>
       </c>
       <c r="I21" t="n">
-        <v>0.741</v>
+        <v>1.6846</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2488</v>
+        <v>1.8506</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0173</v>
+        <v>0.4137</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2315</v>
+        <v>1.4369</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.199</v>
+        <v>-0.2703</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7086</v>
+        <v>-0.518</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4904</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>-4.5526</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4857</v>
+        <v>-0.2274</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6472</v>
+        <v>-0.1326</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1615</v>
+        <v>-0.0948</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9612</v>
+        <v>-2.1893</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0944</v>
+        <v>-0.963</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8668</v>
+        <v>-1.2264</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3186</v>
+        <v>0.0567</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4704</v>
+        <v>-0.6867</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7889</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1758</v>
+        <v>1.2461</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1012</v>
+        <v>0.0172</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>1.2288</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4944</v>
+        <v>-1.1893</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6308</v>
+        <v>-0.7039</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8636</v>
+        <v>-0.4854</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7864</v>
+        <v>0.2579</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2249</v>
+        <v>0.2949</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4386</v>
+        <v>-0.037</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0524</v>
+        <v>-2.5884</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9047</v>
+        <v>-1.0571</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1478</v>
+        <v>-1.5313</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5658</v>
+        <v>-0.3123</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1215</v>
+        <v>0.471</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6873</v>
+        <v>-0.7833</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8655</v>
+        <v>1.1636</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4156</v>
+        <v>1.0892</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4499</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2998</v>
+        <v>-1.4759</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5371</v>
+        <v>-0.6182</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2373</v>
+        <v>-0.8578</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.6293</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0815</v>
+        <v>0.1579</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4869</v>
+        <v>0.2832</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5946</v>
+        <v>-0.1253</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6911</v>
+        <v>-3.3412</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0044</v>
+        <v>0.6317</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6867</v>
+        <v>-3.9729</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1529</v>
+        <v>-1.3342</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9365</v>
+        <v>-0.2902</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7837</v>
+        <v>-1.0439</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8204</v>
+        <v>1.6168</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8977</v>
+        <v>0.3135</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.07729999999999999</v>
+        <v>1.3033</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6675</v>
+        <v>-2.951</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.6037</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7063</v>
+        <v>-2.3472</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.1757</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-1.5934</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4243</v>
+        <v>0.4482</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5777</v>
+        <v>0.6083</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1534</v>
+        <v>-0.1601</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7744</v>
+        <v>-4.0305</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4092</v>
+        <v>-1.2709</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.1836</v>
+        <v>-2.7596</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.3431</v>
+        <v>0.1516</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.293</v>
+        <v>0.9336</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0502</v>
+        <v>-0.782</v>
       </c>
       <c r="J25" t="n">
-        <v>1.628</v>
+        <v>1.7999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3219</v>
+        <v>1.8821</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3061</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.9711</v>
+        <v>-1.6483</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6149</v>
+        <v>-0.9485</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.3563</v>
+        <v>-0.6998</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.361</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.5878</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0224</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.369</v>
+        <v>0.3436</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3466</v>
+        <v>-0.2494</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.1648</v>
+        <v>-5.7319</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5611</v>
+        <v>-1.9942</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.6037</v>
+        <v>-3.7378</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.7343</v>
+        <v>-4.7311</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.0261</v>
+        <v>-2.0167</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.7082</v>
+        <v>-2.7144</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5748</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1785</v>
+        <v>0.1632</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.1783</v>
+        <v>-4.1563</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.8867</v>
+        <v>-2.8775</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2284</v>
+        <v>0.2056</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4174</v>
+        <v>0.174</v>
       </c>
       <c r="U26" t="n">
-        <v>0.189</v>
+        <v>0.0316</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.2628</v>
+        <v>-8.659899999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>6.001699999999998</v>
+        <v>5.724399999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.2649</v>
+        <v>-14.3846</v>
       </c>
       <c r="G27" t="n">
-        <v>2.405400000000001</v>
+        <v>2.502300000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.1787</v>
+        <v>-4.0971</v>
       </c>
       <c r="I27" t="n">
-        <v>6.584000000000001</v>
+        <v>6.599500000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>17.4255</v>
+        <v>17.2461</v>
       </c>
       <c r="K27" t="n">
-        <v>3.392300000000001</v>
+        <v>3.307600000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>14.0334</v>
+        <v>13.9386</v>
       </c>
       <c r="M27" t="n">
-        <v>-15.0202</v>
+        <v>-14.7436</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.571</v>
+        <v>-7.4046</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.449299999999999</v>
+        <v>-7.339</v>
       </c>
       <c r="P27" t="n">
-        <v>-17.0125</v>
+        <v>-17.0723</v>
       </c>
       <c r="Q27" t="n">
-        <v>-22.6833</v>
+        <v>-22.763</v>
       </c>
       <c r="R27" t="n">
-        <v>5.6707</v>
+        <v>5.6907</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6805000000000001</v>
+        <v>2.2544</v>
       </c>
       <c r="T27" t="n">
-        <v>2.646400000000001</v>
+        <v>2.6686</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.9662</v>
+        <v>-0.4140999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>3.6636</v>
+        <v>3.6553</v>
       </c>
       <c r="W27" t="n">
-        <v>8.613099999999999</v>
+        <v>8.572900000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.9495</v>
+        <v>-4.9176</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104497_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104497_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.572800000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104497_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.9176</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
